--- a/data/50001588 - ZITRON PERU HUARON.xlsx
+++ b/data/50001588 - ZITRON PERU HUARON.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="417">
   <si>
     <t xml:space="preserve"> 50001588 - "ZITRON PERU HUARON"</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>Plano Definitivos  OT 4390 ,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217347014202347</t>
@@ -3978,7 +3981,7 @@
         <v>46252.607408854165</v>
       </c>
       <c r="D40" s="5">
-        <v>46252.607631516206</v>
+        <v>46261.18827159722</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>139</v>
@@ -4022,8 +4025,8 @@
       <c r="R40" s="5">
         <v>46251</v>
       </c>
-      <c r="S40" s="7" t="s">
-        <v>64</v>
+      <c r="S40" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -4034,7 +4037,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B41" s="9">
         <v>46244.8163515162</v>
@@ -4046,7 +4049,7 @@
         <v>46255.497544375</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4079,7 +4082,7 @@
         <v>139</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q41" s="9">
         <v>46310</v>
@@ -4099,7 +4102,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B42" s="5">
         <v>46244.81636226852</v>
@@ -4117,10 +4120,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I42" s="5">
         <v>46311</v>
@@ -4141,10 +4144,10 @@
         <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q42" s="5">
         <v>46311</v>
@@ -4164,7 +4167,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B43" s="9">
         <v>46244.8164441088</v>
@@ -4174,16 +4177,16 @@
         <v>46244.91261612269</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="9">
         <v>46385</v>
@@ -4204,10 +4207,10 @@
         <v>136</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="9">
         <v>46385</v>
@@ -4227,7 +4230,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46244.816457824076</v>
@@ -4237,16 +4240,16 @@
         <v>46244.91275376157</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46385</v>
@@ -4264,13 +4267,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4280,7 +4283,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46244.81646045139</v>
@@ -4290,16 +4293,16 @@
         <v>46244.91275005787</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I45" s="9">
         <v>46385</v>
@@ -4317,13 +4320,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4333,7 +4336,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46244.81647885416</v>
@@ -4343,16 +4346,16 @@
         <v>46244.91274583334</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46385</v>
@@ -4370,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4386,7 +4389,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" s="9">
         <v>46244.81648188658</v>
@@ -4396,16 +4399,16 @@
         <v>46244.91274209491</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I47" s="9">
         <v>46385</v>
@@ -4423,13 +4426,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4439,7 +4442,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5">
         <v>46244.8164849537</v>
@@ -4449,16 +4452,16 @@
         <v>46244.91273836806</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I48" s="5">
         <v>46385</v>
@@ -4476,13 +4479,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4492,7 +4495,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B49" s="9">
         <v>46244.81648784722</v>
@@ -4502,16 +4505,16 @@
         <v>46244.9127344213</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I49" s="9">
         <v>46385</v>
@@ -4529,13 +4532,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4545,7 +4548,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B50" s="5">
         <v>46244.81649077546</v>
@@ -4555,16 +4558,16 @@
         <v>46244.91273091435</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I50" s="5">
         <v>46385</v>
@@ -4582,13 +4585,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4598,7 +4601,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B51" s="9">
         <v>46244.81649361111</v>
@@ -4608,16 +4611,16 @@
         <v>46244.912727083334</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I51" s="9">
         <v>46385</v>
@@ -4635,13 +4638,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4651,7 +4654,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" s="5">
         <v>46244.816496458334</v>
@@ -4661,16 +4664,16 @@
         <v>46244.91272341435</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I52" s="5">
         <v>46385</v>
@@ -4688,13 +4691,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4704,7 +4707,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B53" s="9">
         <v>46244.81654564815</v>
@@ -4714,7 +4717,7 @@
         <v>46244.891335636574</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4738,7 +4741,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4751,7 +4754,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B54" s="5">
         <v>46244.8165491088</v>
@@ -4761,16 +4764,16 @@
         <v>46244.91280092593</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I54" s="5">
         <v>46329</v>
@@ -4788,13 +4791,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q54" s="5">
         <v>46330</v>
@@ -4814,7 +4817,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B55" s="9">
         <v>46244.816554606485</v>
@@ -4824,16 +4827,16 @@
         <v>46244.91279732639</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I55" s="9">
         <v>46329</v>
@@ -4851,13 +4854,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>98</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q55" s="9">
         <v>46330</v>
@@ -4877,7 +4880,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B56" s="5">
         <v>46244.81655952546</v>
@@ -4887,16 +4890,16 @@
         <v>46244.91279375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I56" s="5">
         <v>46329</v>
@@ -4914,13 +4917,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q56" s="5">
         <v>46330</v>
@@ -4940,7 +4943,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B57" s="9">
         <v>46244.816564849534</v>
@@ -4950,7 +4953,7 @@
         <v>46244.912869085645</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4977,13 +4980,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q57" s="9">
         <v>46332</v>
@@ -5003,7 +5006,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B58" s="5">
         <v>46244.81657001158</v>
@@ -5013,7 +5016,7 @@
         <v>46244.91286498842</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5040,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q58" s="5">
         <v>46332</v>
@@ -5066,7 +5069,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B59" s="9">
         <v>46244.81657494213</v>
@@ -5076,7 +5079,7 @@
         <v>46244.91286064815</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5103,13 +5106,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q59" s="9">
         <v>46332</v>
@@ -5129,7 +5132,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B60" s="5">
         <v>46244.81658003472</v>
@@ -5139,7 +5142,7 @@
         <v>46244.89240412037</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5163,7 +5166,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5176,7 +5179,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B61" s="9">
         <v>46244.816582893516</v>
@@ -5186,16 +5189,16 @@
         <v>46244.91294087963</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I61" s="9">
         <v>46335</v>
@@ -5213,13 +5216,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q61" s="9">
         <v>46343</v>
@@ -5239,7 +5242,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B62" s="5">
         <v>46244.81659052083</v>
@@ -5249,16 +5252,16 @@
         <v>46244.9130894213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I62" s="5">
         <v>46344</v>
@@ -5276,13 +5279,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q62" s="5">
         <v>46363</v>
@@ -5302,7 +5305,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B63" s="9">
         <v>46244.81665267361</v>
@@ -5312,16 +5315,16 @@
         <v>46255.49758390046</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I63" s="9">
         <v>46344</v>
@@ -5339,13 +5342,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5355,7 +5358,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B64" s="5">
         <v>46244.81666067129</v>
@@ -5365,16 +5368,16 @@
         <v>46255.49758956018</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I64" s="5">
         <v>46344</v>
@@ -5392,13 +5395,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5408,7 +5411,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B65" s="9">
         <v>46244.81666673611</v>
@@ -5418,16 +5421,16 @@
         <v>46255.49758998843</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I65" s="9">
         <v>46344</v>
@@ -5445,13 +5448,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5461,7 +5464,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B66" s="5">
         <v>46244.81667273148</v>
@@ -5471,16 +5474,16 @@
         <v>46255.497587060185</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I66" s="5">
         <v>46344</v>
@@ -5498,13 +5501,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5514,7 +5517,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B67" s="9">
         <v>46244.816676875</v>
@@ -5524,16 +5527,16 @@
         <v>46255.497590486106</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I67" s="9">
         <v>46344</v>
@@ -5551,13 +5554,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5567,7 +5570,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B68" s="5">
         <v>46244.81668157407</v>
@@ -5577,16 +5580,16 @@
         <v>46255.49759086806</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I68" s="5">
         <v>46344</v>
@@ -5604,13 +5607,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5620,7 +5623,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B69" s="9">
         <v>46244.816685949074</v>
@@ -5630,16 +5633,16 @@
         <v>46255.497584791665</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I69" s="9">
         <v>46344</v>
@@ -5657,13 +5660,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5673,7 +5676,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B70" s="5">
         <v>46244.81669008102</v>
@@ -5683,16 +5686,16 @@
         <v>46255.49758743055</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I70" s="5">
         <v>46344</v>
@@ -5710,13 +5713,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5726,7 +5729,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B71" s="9">
         <v>46244.81669421296</v>
@@ -5736,16 +5739,16 @@
         <v>46255.49758538195</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I71" s="9">
         <v>46344</v>
@@ -5763,13 +5766,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5779,7 +5782,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B72" s="5">
         <v>46244.81677893519</v>
@@ -5789,7 +5792,7 @@
         <v>46244.9132377662</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5816,13 +5819,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q72" s="5">
         <v>46364</v>
@@ -5842,7 +5845,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B73" s="9">
         <v>46244.81678523148</v>
@@ -5852,7 +5855,7 @@
         <v>46255.49758440972</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5879,13 +5882,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5895,7 +5898,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B74" s="5">
         <v>46244.8167902662</v>
@@ -5905,7 +5908,7 @@
         <v>46255.497585798614</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5932,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5948,7 +5951,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B75" s="9">
         <v>46244.816795266204</v>
@@ -5958,7 +5961,7 @@
         <v>46255.49759126158</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5985,13 +5988,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6001,7 +6004,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B76" s="5">
         <v>46244.81680001157</v>
@@ -6011,7 +6014,7 @@
         <v>46244.91322800926</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6038,13 +6041,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6054,7 +6057,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B77" s="9">
         <v>46244.81698878472</v>
@@ -6064,7 +6067,7 @@
         <v>46255.49759158565</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6091,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6107,7 +6110,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B78" s="5">
         <v>46244.81699388889</v>
@@ -6117,7 +6120,7 @@
         <v>46255.49759194444</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6144,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6160,7 +6163,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B79" s="9">
         <v>46244.81699806713</v>
@@ -6170,7 +6173,7 @@
         <v>46255.497586701385</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6197,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6213,7 +6216,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B80" s="5">
         <v>46244.817002615746</v>
@@ -6223,7 +6226,7 @@
         <v>46244.91321115741</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6250,13 +6253,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6266,7 +6269,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B81" s="9">
         <v>46244.81700671296</v>
@@ -6276,7 +6279,7 @@
         <v>46255.49758633102</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6303,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6319,7 +6322,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B82" s="5">
         <v>46244.81707873843</v>
@@ -6329,7 +6332,7 @@
         <v>46244.899137534725</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6353,7 +6356,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6366,7 +6369,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B83" s="9">
         <v>46244.81708195602</v>
@@ -6376,16 +6379,16 @@
         <v>46253.19962429398</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I83" s="9">
         <v>46251</v>
@@ -6403,13 +6406,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>53</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q83" s="9">
         <v>46252</v>
@@ -6429,7 +6432,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B84" s="5">
         <v>46244.81709082176</v>
@@ -6439,16 +6442,16 @@
         <v>46244.913301747685</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I84" s="5">
         <v>46331</v>
@@ -6466,13 +6469,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q84" s="5">
         <v>46332</v>
@@ -6492,7 +6495,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B85" s="9">
         <v>46244.817099050924</v>
@@ -6502,16 +6505,16 @@
         <v>46244.913297962965</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I85" s="9">
         <v>46339</v>
@@ -6529,13 +6532,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>131</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q85" s="9">
         <v>46342</v>
@@ -6555,7 +6558,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B86" s="5">
         <v>46244.81710746528</v>
@@ -6565,7 +6568,7 @@
         <v>46244.90714224537</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>25</v>
@@ -6589,7 +6592,7 @@
         <v>26</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6602,7 +6605,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B87" s="9">
         <v>46244.817151041665</v>
@@ -6612,7 +6615,7 @@
         <v>46244.91339998842</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6639,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q87" s="9">
         <v>46373</v>
@@ -6665,7 +6668,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B88" s="5">
         <v>46244.81715847222</v>
@@ -6675,7 +6678,7 @@
         <v>46244.9135178125</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6702,13 +6705,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6718,7 +6721,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B89" s="9">
         <v>46244.817162719904</v>
@@ -6728,7 +6731,7 @@
         <v>46244.91351362268</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6755,13 +6758,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6771,7 +6774,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B90" s="5">
         <v>46244.8171668287</v>
@@ -6781,7 +6784,7 @@
         <v>46244.9135097338</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6808,13 +6811,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6824,7 +6827,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B91" s="9">
         <v>46244.817171076385</v>
@@ -6834,7 +6837,7 @@
         <v>46244.913505613426</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6861,13 +6864,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6877,7 +6880,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B92" s="5">
         <v>46244.81718042824</v>
@@ -6887,7 +6890,7 @@
         <v>46244.91350200231</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6914,13 +6917,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6930,7 +6933,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B93" s="9">
         <v>46244.817183900464</v>
@@ -6940,7 +6943,7 @@
         <v>46244.91349824074</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6967,13 +6970,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6983,7 +6986,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B94" s="5">
         <v>46244.81718719908</v>
@@ -6993,7 +6996,7 @@
         <v>46244.913494374996</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7020,13 +7023,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7036,7 +7039,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B95" s="9">
         <v>46244.817190393514</v>
@@ -7046,7 +7049,7 @@
         <v>46244.91349070602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7073,13 +7076,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7089,7 +7092,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B96" s="5">
         <v>46244.81719398148</v>
@@ -7099,7 +7102,7 @@
         <v>46244.913486481484</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7126,13 +7129,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7142,7 +7145,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B97" s="9">
         <v>46244.81725115741</v>
@@ -7152,7 +7155,7 @@
         <v>46244.91339607639</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7179,13 +7182,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q97" s="9">
         <v>46374</v>
@@ -7205,7 +7208,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B98" s="5">
         <v>46244.81726106482</v>
@@ -7215,7 +7218,7 @@
         <v>46244.91364895833</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7242,13 +7245,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7258,7 +7261,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B99" s="9">
         <v>46244.81726664352</v>
@@ -7268,7 +7271,7 @@
         <v>46244.91364475695</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7295,13 +7298,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7311,7 +7314,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B100" s="5">
         <v>46244.81727153935</v>
@@ -7321,7 +7324,7 @@
         <v>46244.913640659724</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7348,13 +7351,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7364,7 +7367,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B101" s="9">
         <v>46244.81728202546</v>
@@ -7374,7 +7377,7 @@
         <v>46244.91363607639</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7401,13 +7404,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7417,7 +7420,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B102" s="5">
         <v>46244.817287094906</v>
@@ -7427,7 +7430,7 @@
         <v>46244.91363134259</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7454,13 +7457,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7470,7 +7473,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B103" s="9">
         <v>46244.81729128472</v>
@@ -7480,7 +7483,7 @@
         <v>46244.91362707176</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7507,13 +7510,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7523,7 +7526,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B104" s="5">
         <v>46244.81729578704</v>
@@ -7533,7 +7536,7 @@
         <v>46244.91362236111</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7560,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7576,7 +7579,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B105" s="9">
         <v>46244.81730028935</v>
@@ -7586,7 +7589,7 @@
         <v>46244.91361798611</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7613,13 +7616,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7629,7 +7632,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B106" s="5">
         <v>46244.81730454861</v>
@@ -7639,7 +7642,7 @@
         <v>46244.91361362269</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7666,13 +7669,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7682,7 +7685,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B107" s="9">
         <v>46244.81742753473</v>
@@ -7692,7 +7695,7 @@
         <v>46244.913392083334</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7719,13 +7722,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q107" s="9">
         <v>46377</v>
@@ -7745,7 +7748,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B108" s="5">
         <v>46244.81743409722</v>
@@ -7755,7 +7758,7 @@
         <v>46244.91374960648</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7782,13 +7785,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7798,7 +7801,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B109" s="9">
         <v>46244.817438819446</v>
@@ -7808,7 +7811,7 @@
         <v>46244.91374587963</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7835,13 +7838,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7851,7 +7854,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B110" s="5">
         <v>46244.81744333333</v>
@@ -7861,7 +7864,7 @@
         <v>46244.91374239583</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7888,13 +7891,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7904,7 +7907,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B111" s="9">
         <v>46244.81744813657</v>
@@ -7914,7 +7917,7 @@
         <v>46244.913738483796</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7941,13 +7944,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7957,7 +7960,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B112" s="5">
         <v>46244.81745298611</v>
@@ -7967,7 +7970,7 @@
         <v>46244.91373516204</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7994,13 +7997,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8010,7 +8013,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B113" s="9">
         <v>46244.817456875</v>
@@ -8020,7 +8023,7 @@
         <v>46244.91373155093</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8047,13 +8050,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8063,7 +8066,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B114" s="5">
         <v>46244.81745974537</v>
@@ -8073,7 +8076,7 @@
         <v>46244.913727569445</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8100,13 +8103,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8116,7 +8119,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B115" s="9">
         <v>46244.817462719904</v>
@@ -8126,7 +8129,7 @@
         <v>46244.91372370371</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8153,13 +8156,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8169,7 +8172,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B116" s="5">
         <v>46244.81746571759</v>
@@ -8179,7 +8182,7 @@
         <v>46244.91371995371</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8206,13 +8209,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8222,7 +8225,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B117" s="9">
         <v>46244.81758990741</v>
@@ -8232,7 +8235,7 @@
         <v>46244.91338834491</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8259,13 +8262,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q117" s="9">
         <v>46378</v>
@@ -8285,7 +8288,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B118" s="5">
         <v>46244.81759976852</v>
@@ -8295,7 +8298,7 @@
         <v>46244.91387160879</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8322,13 +8325,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8338,7 +8341,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B119" s="9">
         <v>46244.81760425926</v>
@@ -8348,7 +8351,7 @@
         <v>46244.91386771991</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8375,13 +8378,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8391,7 +8394,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B120" s="5">
         <v>46244.81760835648</v>
@@ -8401,7 +8404,7 @@
         <v>46244.91386390047</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8428,13 +8431,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8444,7 +8447,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B121" s="9">
         <v>46244.81761269676</v>
@@ -8454,7 +8457,7 @@
         <v>46244.91385996528</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8481,13 +8484,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8497,7 +8500,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B122" s="5">
         <v>46244.81761719908</v>
@@ -8507,7 +8510,7 @@
         <v>46244.913855798615</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8534,13 +8537,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8550,7 +8553,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B123" s="9">
         <v>46244.81762068287</v>
@@ -8560,7 +8563,7 @@
         <v>46244.913851805555</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8587,13 +8590,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8603,7 +8606,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B124" s="5">
         <v>46244.81762393519</v>
@@ -8613,7 +8616,7 @@
         <v>46244.91384795139</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8640,13 +8643,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8656,7 +8659,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B125" s="9">
         <v>46244.81762652777</v>
@@ -8666,7 +8669,7 @@
         <v>46244.91384385417</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8693,13 +8696,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8709,7 +8712,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B126" s="5">
         <v>46244.81762986111</v>
@@ -8719,7 +8722,7 @@
         <v>46244.91383961806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8746,13 +8749,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8762,7 +8765,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B127" s="9">
         <v>46244.81768571759</v>
@@ -8772,7 +8775,7 @@
         <v>46244.91338439815</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8799,13 +8802,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q127" s="9">
         <v>46379</v>
@@ -8825,7 +8828,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B128" s="5">
         <v>46244.81769393518</v>
@@ -8835,7 +8838,7 @@
         <v>46244.91398324074</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8862,13 +8865,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8878,7 +8881,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B129" s="9">
         <v>46244.817696770835</v>
@@ -8888,7 +8891,7 @@
         <v>46244.91397908565</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8915,13 +8918,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8931,7 +8934,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B130" s="5">
         <v>46244.81770020833</v>
@@ -8941,7 +8944,7 @@
         <v>46244.913975</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8968,13 +8971,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8984,7 +8987,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B131" s="9">
         <v>46244.81770377315</v>
@@ -8994,7 +8997,7 @@
         <v>46244.91397079861</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9021,13 +9024,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9037,7 +9040,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B132" s="5">
         <v>46244.8177063426</v>
@@ -9047,7 +9050,7 @@
         <v>46244.913967071756</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9074,13 +9077,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9090,7 +9093,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B133" s="9">
         <v>46244.817751400464</v>
@@ -9100,7 +9103,7 @@
         <v>46244.913963541665</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9127,13 +9130,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9143,7 +9146,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B134" s="5">
         <v>46244.817755393524</v>
@@ -9153,7 +9156,7 @@
         <v>46244.91395974537</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9180,13 +9183,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9196,7 +9199,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B135" s="9">
         <v>46244.81775805556</v>
@@ -9206,7 +9209,7 @@
         <v>46244.91395638889</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9233,13 +9236,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9249,7 +9252,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B136" s="5">
         <v>46244.81776177083</v>
@@ -9259,7 +9262,7 @@
         <v>46244.91395271991</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9286,13 +9289,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9302,7 +9305,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B137" s="9">
         <v>46244.81781928241</v>
@@ -9312,7 +9315,7 @@
         <v>46244.913380405094</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9339,10 +9342,10 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>26</v>
@@ -9365,7 +9368,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B138" s="5">
         <v>46244.81782405093</v>
@@ -9375,7 +9378,7 @@
         <v>46244.91410258102</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9402,13 +9405,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9418,7 +9421,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B139" s="9">
         <v>46244.81782776621</v>
@@ -9428,7 +9431,7 @@
         <v>46244.91409853009</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9455,13 +9458,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9471,7 +9474,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B140" s="5">
         <v>46244.817832500004</v>
@@ -9481,7 +9484,7 @@
         <v>46244.91409476852</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9508,13 +9511,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9524,7 +9527,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B141" s="9">
         <v>46244.81783613426</v>
@@ -9534,7 +9537,7 @@
         <v>46244.914091099534</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9561,13 +9564,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9577,7 +9580,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B142" s="5">
         <v>46244.817840069445</v>
@@ -9587,7 +9590,7 @@
         <v>46244.91408688657</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9614,13 +9617,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9630,7 +9633,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B143" s="9">
         <v>46244.81784383101</v>
@@ -9640,7 +9643,7 @@
         <v>46244.914082476855</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9667,13 +9670,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9683,7 +9686,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B144" s="5">
         <v>46244.81784768519</v>
@@ -9693,7 +9696,7 @@
         <v>46244.91407861111</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9720,13 +9723,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9736,7 +9739,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B145" s="9">
         <v>46244.817851354164</v>
@@ -9746,7 +9749,7 @@
         <v>46244.914074375</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -9773,13 +9776,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9789,7 +9792,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B146" s="5">
         <v>46244.81785493056</v>
@@ -9799,7 +9802,7 @@
         <v>46244.91407049769</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -9826,13 +9829,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9842,7 +9845,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B147" s="9">
         <v>46244.81796724537</v>
@@ -9852,7 +9855,7 @@
         <v>46244.91337646991</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -9879,13 +9882,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q147" s="9">
         <v>46386</v>
@@ -9905,7 +9908,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B148" s="5">
         <v>46244.817975972226</v>
@@ -9915,7 +9918,7 @@
         <v>46244.914202106476</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -9942,13 +9945,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9958,7 +9961,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B149" s="9">
         <v>46244.81797934028</v>
@@ -9968,7 +9971,7 @@
         <v>46244.914198506944</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -9995,13 +9998,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10011,7 +10014,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B150" s="5">
         <v>46244.81798270834</v>
@@ -10021,7 +10024,7 @@
         <v>46244.9141949537</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10048,13 +10051,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10064,7 +10067,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B151" s="9">
         <v>46244.81798604167</v>
@@ -10074,7 +10077,7 @@
         <v>46244.9141912037</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10101,13 +10104,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10117,7 +10120,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B152" s="5">
         <v>46244.81798946759</v>
@@ -10127,7 +10130,7 @@
         <v>46244.91418792824</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10154,13 +10157,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10170,7 +10173,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B153" s="9">
         <v>46244.81799275463</v>
@@ -10180,7 +10183,7 @@
         <v>46244.91418486111</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10207,13 +10210,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10223,7 +10226,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B154" s="5">
         <v>46244.81799599537</v>
@@ -10233,7 +10236,7 @@
         <v>46244.91418086806</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10260,13 +10263,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10276,7 +10279,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B155" s="9">
         <v>46244.81799964121</v>
@@ -10286,7 +10289,7 @@
         <v>46244.9141775</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10313,13 +10316,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10329,7 +10332,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B156" s="5">
         <v>46244.81800288195</v>
@@ -10339,7 +10342,7 @@
         <v>46244.914173240744</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10366,13 +10369,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10382,7 +10385,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B157" s="9">
         <v>46244.818105659724</v>
@@ -10392,7 +10395,7 @@
         <v>46244.909393634254</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>25</v>
@@ -10416,7 +10419,7 @@
         <v>26</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10429,7 +10432,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B158" s="5">
         <v>46244.81810916666</v>
@@ -10439,16 +10442,16 @@
         <v>46244.91432081019</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I158" s="5">
         <v>46391</v>
@@ -10466,13 +10469,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q158" s="5">
         <v>46391</v>
@@ -10492,7 +10495,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B159" s="9">
         <v>46244.81811532407</v>
@@ -10502,16 +10505,16 @@
         <v>46244.91432297454</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I159" s="9">
         <v>46391</v>
@@ -10529,13 +10532,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10545,7 +10548,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B160" s="5">
         <v>46244.818118703704</v>
@@ -10555,16 +10558,16 @@
         <v>46244.91431875</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I160" s="5">
         <v>46391</v>
@@ -10582,13 +10585,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10598,7 +10601,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B161" s="9">
         <v>46244.8181217824</v>
@@ -10608,16 +10611,16 @@
         <v>46244.9143146412</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I161" s="9">
         <v>46391</v>
@@ -10635,13 +10638,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10651,7 +10654,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B162" s="5">
         <v>46244.81812486111</v>
@@ -10661,16 +10664,16 @@
         <v>46244.91431086806</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I162" s="5">
         <v>46391</v>
@@ -10688,13 +10691,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10704,7 +10707,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B163" s="9">
         <v>46244.81812762731</v>
@@ -10714,16 +10717,16 @@
         <v>46244.91430675926</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I163" s="9">
         <v>46391</v>
@@ -10741,13 +10744,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10757,7 +10760,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B164" s="5">
         <v>46244.81813112268</v>
@@ -10767,16 +10770,16 @@
         <v>46244.91430280093</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I164" s="5">
         <v>46391</v>
@@ -10794,13 +10797,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10810,7 +10813,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B165" s="9">
         <v>46244.81813422454</v>
@@ -10820,16 +10823,16 @@
         <v>46244.9142987963</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I165" s="9">
         <v>46391</v>
@@ -10847,13 +10850,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -10863,7 +10866,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B166" s="5">
         <v>46244.818137395836</v>
@@ -10873,16 +10876,16 @@
         <v>46244.91429494213</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I166" s="5">
         <v>46391</v>
@@ -10900,13 +10903,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -10916,7 +10919,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B167" s="9">
         <v>46244.818140937496</v>
@@ -10926,16 +10929,16 @@
         <v>46244.91429079861</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I167" s="9">
         <v>46391</v>
@@ -10953,13 +10956,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -10969,7 +10972,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B168" s="5">
         <v>46244.8182020949</v>
@@ -10979,7 +10982,7 @@
         <v>46244.91455590278</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11006,10 +11009,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11032,7 +11035,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B169" s="9">
         <v>46244.81820765046</v>
@@ -11042,7 +11045,7 @@
         <v>46244.91455376157</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11069,13 +11072,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11085,7 +11088,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B170" s="5">
         <v>46244.818210717596</v>
@@ -11095,7 +11098,7 @@
         <v>46244.91454974537</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11122,13 +11125,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11138,7 +11141,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B171" s="9">
         <v>46244.8182140162</v>
@@ -11148,7 +11151,7 @@
         <v>46244.91454637732</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11175,13 +11178,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11191,7 +11194,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B172" s="5">
         <v>46244.818217210646</v>
@@ -11201,7 +11204,7 @@
         <v>46244.914542928236</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11228,13 +11231,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11244,7 +11247,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B173" s="9">
         <v>46244.818220671295</v>
@@ -11254,7 +11257,7 @@
         <v>46244.914539108795</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11281,13 +11284,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11297,7 +11300,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B174" s="5">
         <v>46244.81822380787</v>
@@ -11307,7 +11310,7 @@
         <v>46244.914535601856</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11334,13 +11337,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11350,7 +11353,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B175" s="9">
         <v>46244.818227094904</v>
@@ -11360,7 +11363,7 @@
         <v>46244.91453206018</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11387,13 +11390,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11403,7 +11406,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B176" s="5">
         <v>46244.81823046296</v>
@@ -11413,7 +11416,7 @@
         <v>46244.91452826389</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11440,13 +11443,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11456,7 +11459,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B177" s="9">
         <v>46244.81823376157</v>
@@ -11466,7 +11469,7 @@
         <v>46244.91452491898</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11493,13 +11496,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11509,7 +11512,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B178" s="5">
         <v>46244.8183515625</v>
@@ -11519,16 +11522,16 @@
         <v>46244.91482409722</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I178" s="5">
         <v>46393</v>
@@ -11546,13 +11549,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q178" s="5">
         <v>46393</v>
@@ -11572,7 +11575,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B179" s="9">
         <v>46244.8183578125</v>
@@ -11582,16 +11585,16 @@
         <v>46244.91479045139</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H179" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I179" s="9">
         <v>46393</v>
@@ -11609,13 +11612,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11625,7 +11628,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B180" s="5">
         <v>46244.81836063658</v>
@@ -11635,16 +11638,16 @@
         <v>46244.914786828704</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I180" s="5">
         <v>46393</v>
@@ -11662,13 +11665,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11678,7 +11681,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B181" s="9">
         <v>46244.81836416667</v>
@@ -11688,16 +11691,16 @@
         <v>46244.91478277778</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H181" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I181" s="9">
         <v>46393</v>
@@ -11715,13 +11718,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11731,7 +11734,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B182" s="5">
         <v>46244.81836775463</v>
@@ -11741,16 +11744,16 @@
         <v>46244.914779108796</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I182" s="5">
         <v>46393</v>
@@ -11768,13 +11771,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -11784,7 +11787,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B183" s="9">
         <v>46244.81837119213</v>
@@ -11794,16 +11797,16 @@
         <v>46244.91477552083</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H183" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I183" s="9">
         <v>46393</v>
@@ -11821,13 +11824,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -11837,7 +11840,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B184" s="5">
         <v>46244.8183746412</v>
@@ -11847,16 +11850,16 @@
         <v>46244.91477159722</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I184" s="5">
         <v>46393</v>
@@ -11874,13 +11877,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -11890,7 +11893,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B185" s="9">
         <v>46244.81837791667</v>
@@ -11900,16 +11903,16 @@
         <v>46244.91476724537</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H185" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I185" s="9">
         <v>46393</v>
@@ -11927,13 +11930,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -11943,7 +11946,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B186" s="5">
         <v>46244.81838135417</v>
@@ -11953,16 +11956,16 @@
         <v>46244.91476313658</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I186" s="5">
         <v>46393</v>
@@ -11980,13 +11983,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -11996,7 +11999,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B187" s="9">
         <v>46244.81838474537</v>
@@ -12006,16 +12009,16 @@
         <v>46244.914758240746</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H187" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I187" s="9">
         <v>46393</v>
@@ -12033,13 +12036,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12049,7 +12052,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B188" s="5">
         <v>46244.818483333336</v>
@@ -12059,16 +12062,16 @@
         <v>46244.9149944213</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I188" s="5">
         <v>46394</v>
@@ -12086,13 +12089,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q188" s="5">
         <v>46394</v>
@@ -12112,7 +12115,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B189" s="9">
         <v>46244.81849010417</v>
@@ -12122,16 +12125,16 @@
         <v>46244.914988275465</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H189" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I189" s="9">
         <v>46394</v>
@@ -12149,13 +12152,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12165,7 +12168,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B190" s="5">
         <v>46244.818493750005</v>
@@ -12175,16 +12178,16 @@
         <v>46244.91498451389</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I190" s="5">
         <v>46394</v>
@@ -12202,13 +12205,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12218,7 +12221,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B191" s="9">
         <v>46244.81849773148</v>
@@ -12228,16 +12231,16 @@
         <v>46244.91498094908</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I191" s="9">
         <v>46394</v>
@@ -12255,13 +12258,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12271,7 +12274,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B192" s="5">
         <v>46244.818501284724</v>
@@ -12281,16 +12284,16 @@
         <v>46244.91497737268</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I192" s="5">
         <v>46394</v>
@@ -12308,13 +12311,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12324,7 +12327,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B193" s="9">
         <v>46244.81850474537</v>
@@ -12334,16 +12337,16 @@
         <v>46244.914973680556</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H193" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I193" s="9">
         <v>46394</v>
@@ -12361,13 +12364,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12377,7 +12380,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B194" s="5">
         <v>46244.818508055556</v>
@@ -12387,16 +12390,16 @@
         <v>46244.914969687496</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I194" s="5">
         <v>46394</v>
@@ -12414,13 +12417,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12430,7 +12433,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B195" s="9">
         <v>46244.818511192134</v>
@@ -12440,16 +12443,16 @@
         <v>46244.91496552083</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H195" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I195" s="9">
         <v>46394</v>
@@ -12467,13 +12470,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12483,7 +12486,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B196" s="5">
         <v>46244.81851430556</v>
@@ -12493,16 +12496,16 @@
         <v>46244.91496141204</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I196" s="5">
         <v>46394</v>
@@ -12520,13 +12523,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12536,7 +12539,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B197" s="9">
         <v>46244.81851734954</v>
@@ -12546,16 +12549,16 @@
         <v>46244.91495744213</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H197" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I197" s="9">
         <v>46394</v>
@@ -12573,13 +12576,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12589,7 +12592,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B198" s="5">
         <v>46244.81857152778</v>
@@ -12599,7 +12602,7 @@
         <v>46244.909651319445</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>25</v>
@@ -12623,7 +12626,7 @@
         <v>26</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>26</v>
@@ -12636,7 +12639,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B199" s="9">
         <v>46244.81857427083</v>
@@ -12646,16 +12649,16 @@
         <v>46244.91504364583</v>
       </c>
       <c r="E199" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F199" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H199" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I199" s="9">
         <v>46395</v>
@@ -12673,13 +12676,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q199" s="9">
         <v>46405</v>
@@ -12699,7 +12702,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B200" s="5">
         <v>46244.81869961806</v>
@@ -12709,16 +12712,16 @@
         <v>46244.915039988424</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I200" s="5">
         <v>46395</v>
@@ -12736,13 +12739,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q200" s="5">
         <v>46405</v>

--- a/data/50001588 - ZITRON PERU HUARON.xlsx
+++ b/data/50001588 - ZITRON PERU HUARON.xlsx
@@ -3775,7 +3775,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46244.91247513889</v>
+        <v>46267.169909178236</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>75</v>

--- a/data/50001588 - ZITRON PERU HUARON.xlsx
+++ b/data/50001588 - ZITRON PERU HUARON.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="416">
   <si>
     <t xml:space="preserve"> 50001588 - "ZITRON PERU HUARON"</t>
   </si>
@@ -465,9 +465,6 @@
   </si>
   <si>
     <t>Plano Definitivos  OT 4390 ,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217347014202347</t>
@@ -3983,7 +3980,7 @@
         <v>46252.607408854165</v>
       </c>
       <c r="D40" s="5">
-        <v>46261.18827159722</v>
+        <v>46269.174097650466</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>139</v>
@@ -4027,8 +4024,8 @@
       <c r="R40" s="5">
         <v>46251</v>
       </c>
-      <c r="S40" s="12" t="s">
-        <v>143</v>
+      <c r="S40" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -4039,7 +4036,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B41" s="9">
         <v>46244.8163515162</v>
@@ -4051,7 +4048,7 @@
         <v>46255.497544375</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4084,7 +4081,7 @@
         <v>139</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q41" s="9">
         <v>46310</v>
@@ -4104,7 +4101,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B42" s="5">
         <v>46244.81636226852</v>
@@ -4122,10 +4119,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I42" s="5">
         <v>46311</v>
@@ -4146,10 +4143,10 @@
         <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q42" s="5">
         <v>46311</v>
@@ -4169,7 +4166,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B43" s="9">
         <v>46244.8164441088</v>
@@ -4179,16 +4176,16 @@
         <v>46244.91261612269</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I43" s="9">
         <v>46385</v>
@@ -4209,10 +4206,10 @@
         <v>136</v>
       </c>
       <c r="O43" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="Q43" s="9">
         <v>46385</v>
@@ -4232,7 +4229,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46244.816457824076</v>
@@ -4242,16 +4239,16 @@
         <v>46244.91275376157</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46385</v>
@@ -4269,13 +4266,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4285,7 +4282,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="9">
         <v>46244.81646045139</v>
@@ -4295,16 +4292,16 @@
         <v>46244.91275005787</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I45" s="9">
         <v>46385</v>
@@ -4322,13 +4319,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4338,7 +4335,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46244.81647885416</v>
@@ -4348,16 +4345,16 @@
         <v>46244.91274583334</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I46" s="5">
         <v>46385</v>
@@ -4375,13 +4372,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4391,7 +4388,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B47" s="9">
         <v>46244.81648188658</v>
@@ -4401,16 +4398,16 @@
         <v>46244.91274209491</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I47" s="9">
         <v>46385</v>
@@ -4428,13 +4425,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4444,7 +4441,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B48" s="5">
         <v>46244.8164849537</v>
@@ -4454,16 +4451,16 @@
         <v>46244.91273836806</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I48" s="5">
         <v>46385</v>
@@ -4481,13 +4478,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4497,7 +4494,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B49" s="9">
         <v>46244.81648784722</v>
@@ -4507,16 +4504,16 @@
         <v>46244.9127344213</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I49" s="9">
         <v>46385</v>
@@ -4534,13 +4531,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4550,7 +4547,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B50" s="5">
         <v>46244.81649077546</v>
@@ -4560,16 +4557,16 @@
         <v>46244.91273091435</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I50" s="5">
         <v>46385</v>
@@ -4587,13 +4584,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4603,7 +4600,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B51" s="9">
         <v>46244.81649361111</v>
@@ -4613,16 +4610,16 @@
         <v>46244.912727083334</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="I51" s="9">
         <v>46385</v>
@@ -4640,13 +4637,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4656,7 +4653,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B52" s="5">
         <v>46244.816496458334</v>
@@ -4666,16 +4663,16 @@
         <v>46244.91272341435</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="I52" s="5">
         <v>46385</v>
@@ -4693,13 +4690,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4709,7 +4706,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B53" s="9">
         <v>46244.81654564815</v>
@@ -4719,7 +4716,7 @@
         <v>46244.891335636574</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4743,7 +4740,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4756,7 +4753,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B54" s="5">
         <v>46244.8165491088</v>
@@ -4766,16 +4763,16 @@
         <v>46244.91280092593</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I54" s="5">
         <v>46329</v>
@@ -4793,13 +4790,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>90</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q54" s="5">
         <v>46330</v>
@@ -4819,7 +4816,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B55" s="9">
         <v>46244.816554606485</v>
@@ -4829,16 +4826,16 @@
         <v>46244.91279732639</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I55" s="9">
         <v>46329</v>
@@ -4856,13 +4853,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>98</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q55" s="9">
         <v>46330</v>
@@ -4882,7 +4879,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B56" s="5">
         <v>46244.81655952546</v>
@@ -4892,16 +4889,16 @@
         <v>46244.91279375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I56" s="5">
         <v>46329</v>
@@ -4919,13 +4916,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q56" s="5">
         <v>46330</v>
@@ -4945,7 +4942,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B57" s="9">
         <v>46244.816564849534</v>
@@ -4955,7 +4952,7 @@
         <v>46244.912869085645</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4982,13 +4979,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q57" s="9">
         <v>46332</v>
@@ -5008,7 +5005,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B58" s="5">
         <v>46244.81657001158</v>
@@ -5018,7 +5015,7 @@
         <v>46244.91286498842</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5045,13 +5042,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q58" s="5">
         <v>46332</v>
@@ -5071,7 +5068,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B59" s="9">
         <v>46244.81657494213</v>
@@ -5081,7 +5078,7 @@
         <v>46244.91286064815</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5108,13 +5105,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q59" s="9">
         <v>46332</v>
@@ -5134,7 +5131,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B60" s="5">
         <v>46244.81658003472</v>
@@ -5144,7 +5141,7 @@
         <v>46244.89240412037</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5168,7 +5165,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5181,7 +5178,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B61" s="9">
         <v>46244.816582893516</v>
@@ -5191,16 +5188,16 @@
         <v>46244.91294087963</v>
       </c>
       <c r="E61" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="H61" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I61" s="9">
         <v>46335</v>
@@ -5218,13 +5215,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q61" s="9">
         <v>46343</v>
@@ -5244,7 +5241,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B62" s="5">
         <v>46244.81659052083</v>
@@ -5254,16 +5251,16 @@
         <v>46244.9130894213</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I62" s="5">
         <v>46344</v>
@@ -5281,13 +5278,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q62" s="5">
         <v>46363</v>
@@ -5307,7 +5304,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B63" s="9">
         <v>46244.81665267361</v>
@@ -5317,16 +5314,16 @@
         <v>46255.49758390046</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I63" s="9">
         <v>46344</v>
@@ -5344,13 +5341,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5360,7 +5357,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B64" s="5">
         <v>46244.81666067129</v>
@@ -5370,16 +5367,16 @@
         <v>46255.49758956018</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I64" s="5">
         <v>46344</v>
@@ -5397,13 +5394,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5413,7 +5410,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B65" s="9">
         <v>46244.81666673611</v>
@@ -5423,16 +5420,16 @@
         <v>46255.49758998843</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I65" s="9">
         <v>46344</v>
@@ -5450,13 +5447,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5466,7 +5463,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B66" s="5">
         <v>46244.81667273148</v>
@@ -5476,16 +5473,16 @@
         <v>46255.497587060185</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I66" s="5">
         <v>46344</v>
@@ -5503,13 +5500,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5519,7 +5516,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B67" s="9">
         <v>46244.816676875</v>
@@ -5529,16 +5526,16 @@
         <v>46255.497590486106</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I67" s="9">
         <v>46344</v>
@@ -5556,13 +5553,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5572,7 +5569,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B68" s="5">
         <v>46244.81668157407</v>
@@ -5582,16 +5579,16 @@
         <v>46255.49759086806</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I68" s="5">
         <v>46344</v>
@@ -5609,13 +5606,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5625,7 +5622,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B69" s="9">
         <v>46244.816685949074</v>
@@ -5635,16 +5632,16 @@
         <v>46255.497584791665</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I69" s="9">
         <v>46344</v>
@@ -5662,13 +5659,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5678,7 +5675,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B70" s="5">
         <v>46244.81669008102</v>
@@ -5688,16 +5685,16 @@
         <v>46255.49758743055</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I70" s="5">
         <v>46344</v>
@@ -5715,13 +5712,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5731,7 +5728,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B71" s="9">
         <v>46244.81669421296</v>
@@ -5741,16 +5738,16 @@
         <v>46255.49758538195</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I71" s="9">
         <v>46344</v>
@@ -5768,13 +5765,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5784,7 +5781,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B72" s="5">
         <v>46244.81677893519</v>
@@ -5794,7 +5791,7 @@
         <v>46244.9132377662</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5821,13 +5818,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q72" s="5">
         <v>46364</v>
@@ -5847,7 +5844,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B73" s="9">
         <v>46244.81678523148</v>
@@ -5857,7 +5854,7 @@
         <v>46255.49758440972</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5884,13 +5881,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5900,7 +5897,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B74" s="5">
         <v>46244.8167902662</v>
@@ -5910,7 +5907,7 @@
         <v>46255.497585798614</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5937,13 +5934,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5953,7 +5950,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B75" s="9">
         <v>46244.816795266204</v>
@@ -5963,7 +5960,7 @@
         <v>46255.49759126158</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5990,13 +5987,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6006,7 +6003,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B76" s="5">
         <v>46244.81680001157</v>
@@ -6016,7 +6013,7 @@
         <v>46244.91322800926</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6043,13 +6040,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6059,7 +6056,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B77" s="9">
         <v>46244.81698878472</v>
@@ -6069,7 +6066,7 @@
         <v>46255.49759158565</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6096,13 +6093,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6112,7 +6109,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B78" s="5">
         <v>46244.81699388889</v>
@@ -6122,7 +6119,7 @@
         <v>46255.49759194444</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6149,13 +6146,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6165,7 +6162,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B79" s="9">
         <v>46244.81699806713</v>
@@ -6175,7 +6172,7 @@
         <v>46255.497586701385</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6202,13 +6199,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6218,7 +6215,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B80" s="5">
         <v>46244.817002615746</v>
@@ -6228,7 +6225,7 @@
         <v>46244.91321115741</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6255,13 +6252,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6271,7 +6268,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B81" s="9">
         <v>46244.81700671296</v>
@@ -6281,7 +6278,7 @@
         <v>46255.49758633102</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6308,13 +6305,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O81" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6324,7 +6321,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B82" s="5">
         <v>46244.81707873843</v>
@@ -6334,7 +6331,7 @@
         <v>46244.899137534725</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6358,7 +6355,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6371,7 +6368,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B83" s="9">
         <v>46244.81708195602</v>
@@ -6381,16 +6378,16 @@
         <v>46253.19962429398</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I83" s="9">
         <v>46251</v>
@@ -6408,13 +6405,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>53</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q83" s="9">
         <v>46252</v>
@@ -6434,7 +6431,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B84" s="5">
         <v>46244.81709082176</v>
@@ -6444,16 +6441,16 @@
         <v>46244.913301747685</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I84" s="5">
         <v>46331</v>
@@ -6471,13 +6468,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q84" s="5">
         <v>46332</v>
@@ -6497,7 +6494,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B85" s="9">
         <v>46244.817099050924</v>
@@ -6507,16 +6504,16 @@
         <v>46244.913297962965</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I85" s="9">
         <v>46339</v>
@@ -6534,13 +6531,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>131</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q85" s="9">
         <v>46342</v>
@@ -6560,7 +6557,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B86" s="5">
         <v>46244.81710746528</v>
@@ -6570,7 +6567,7 @@
         <v>46244.90714224537</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>25</v>
@@ -6594,7 +6591,7 @@
         <v>26</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6607,7 +6604,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B87" s="9">
         <v>46244.817151041665</v>
@@ -6617,7 +6614,7 @@
         <v>46244.91339998842</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6644,13 +6641,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q87" s="9">
         <v>46373</v>
@@ -6670,7 +6667,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B88" s="5">
         <v>46244.81715847222</v>
@@ -6680,7 +6677,7 @@
         <v>46244.9135178125</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6707,13 +6704,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6723,7 +6720,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B89" s="9">
         <v>46244.817162719904</v>
@@ -6733,7 +6730,7 @@
         <v>46244.91351362268</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6760,13 +6757,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6776,7 +6773,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B90" s="5">
         <v>46244.8171668287</v>
@@ -6786,7 +6783,7 @@
         <v>46244.9135097338</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6813,13 +6810,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6829,7 +6826,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B91" s="9">
         <v>46244.817171076385</v>
@@ -6839,7 +6836,7 @@
         <v>46244.913505613426</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6866,13 +6863,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6882,7 +6879,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B92" s="5">
         <v>46244.81718042824</v>
@@ -6892,7 +6889,7 @@
         <v>46244.91350200231</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6919,13 +6916,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6935,7 +6932,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B93" s="9">
         <v>46244.817183900464</v>
@@ -6945,7 +6942,7 @@
         <v>46244.91349824074</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6972,13 +6969,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6988,7 +6985,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B94" s="5">
         <v>46244.81718719908</v>
@@ -6998,7 +6995,7 @@
         <v>46244.913494374996</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7025,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7041,7 +7038,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B95" s="9">
         <v>46244.817190393514</v>
@@ -7051,7 +7048,7 @@
         <v>46244.91349070602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7078,13 +7075,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7094,7 +7091,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B96" s="5">
         <v>46244.81719398148</v>
@@ -7104,7 +7101,7 @@
         <v>46244.913486481484</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7131,13 +7128,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7147,7 +7144,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B97" s="9">
         <v>46244.81725115741</v>
@@ -7157,7 +7154,7 @@
         <v>46244.91339607639</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7184,13 +7181,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q97" s="9">
         <v>46374</v>
@@ -7210,7 +7207,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B98" s="5">
         <v>46244.81726106482</v>
@@ -7220,7 +7217,7 @@
         <v>46244.91364895833</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7247,13 +7244,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7263,7 +7260,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B99" s="9">
         <v>46244.81726664352</v>
@@ -7273,7 +7270,7 @@
         <v>46244.91364475695</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7300,13 +7297,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7316,7 +7313,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B100" s="5">
         <v>46244.81727153935</v>
@@ -7326,7 +7323,7 @@
         <v>46244.913640659724</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7353,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7369,7 +7366,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B101" s="9">
         <v>46244.81728202546</v>
@@ -7379,7 +7376,7 @@
         <v>46244.91363607639</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7406,13 +7403,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O101" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="P101" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="P101" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7422,7 +7419,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B102" s="5">
         <v>46244.817287094906</v>
@@ -7432,7 +7429,7 @@
         <v>46244.91363134259</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7459,13 +7456,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7475,7 +7472,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B103" s="9">
         <v>46244.81729128472</v>
@@ -7485,7 +7482,7 @@
         <v>46244.91362707176</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7512,13 +7509,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7528,7 +7525,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B104" s="5">
         <v>46244.81729578704</v>
@@ -7538,7 +7535,7 @@
         <v>46244.91362236111</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7565,13 +7562,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7581,7 +7578,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B105" s="9">
         <v>46244.81730028935</v>
@@ -7591,7 +7588,7 @@
         <v>46244.91361798611</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7618,13 +7615,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7634,7 +7631,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B106" s="5">
         <v>46244.81730454861</v>
@@ -7644,7 +7641,7 @@
         <v>46244.91361362269</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7671,13 +7668,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7687,7 +7684,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B107" s="9">
         <v>46244.81742753473</v>
@@ -7697,7 +7694,7 @@
         <v>46244.913392083334</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7724,13 +7721,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q107" s="9">
         <v>46377</v>
@@ -7750,7 +7747,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B108" s="5">
         <v>46244.81743409722</v>
@@ -7760,7 +7757,7 @@
         <v>46244.91374960648</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7787,13 +7784,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7803,7 +7800,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B109" s="9">
         <v>46244.817438819446</v>
@@ -7813,7 +7810,7 @@
         <v>46244.91374587963</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7840,13 +7837,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7856,7 +7853,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B110" s="5">
         <v>46244.81744333333</v>
@@ -7866,7 +7863,7 @@
         <v>46244.91374239583</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7893,13 +7890,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7909,7 +7906,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B111" s="9">
         <v>46244.81744813657</v>
@@ -7919,7 +7916,7 @@
         <v>46244.913738483796</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7946,13 +7943,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O111" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>286</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>287</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7962,7 +7959,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B112" s="5">
         <v>46244.81745298611</v>
@@ -7972,7 +7969,7 @@
         <v>46244.91373516204</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7999,13 +7996,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8015,7 +8012,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B113" s="9">
         <v>46244.817456875</v>
@@ -8025,7 +8022,7 @@
         <v>46244.91373155093</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8052,13 +8049,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8068,7 +8065,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B114" s="5">
         <v>46244.81745974537</v>
@@ -8078,7 +8075,7 @@
         <v>46244.913727569445</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8105,13 +8102,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8121,7 +8118,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B115" s="9">
         <v>46244.817462719904</v>
@@ -8131,7 +8128,7 @@
         <v>46244.91372370371</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8158,13 +8155,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8174,7 +8171,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B116" s="5">
         <v>46244.81746571759</v>
@@ -8184,7 +8181,7 @@
         <v>46244.91371995371</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8211,13 +8208,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8227,7 +8224,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B117" s="9">
         <v>46244.81758990741</v>
@@ -8237,7 +8234,7 @@
         <v>46244.91338834491</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8264,13 +8261,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O117" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="P117" s="10" t="s">
         <v>295</v>
-      </c>
-      <c r="P117" s="10" t="s">
-        <v>296</v>
       </c>
       <c r="Q117" s="9">
         <v>46378</v>
@@ -8290,7 +8287,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B118" s="5">
         <v>46244.81759976852</v>
@@ -8300,7 +8297,7 @@
         <v>46244.91387160879</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8327,13 +8324,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O118" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="P118" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="P118" s="6" t="s">
-        <v>300</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8343,7 +8340,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B119" s="9">
         <v>46244.81760425926</v>
@@ -8353,7 +8350,7 @@
         <v>46244.91386771991</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8380,13 +8377,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8396,7 +8393,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B120" s="5">
         <v>46244.81760835648</v>
@@ -8406,7 +8403,7 @@
         <v>46244.91386390047</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8433,13 +8430,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8449,7 +8446,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B121" s="9">
         <v>46244.81761269676</v>
@@ -8459,7 +8456,7 @@
         <v>46244.91385996528</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8486,13 +8483,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8502,7 +8499,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B122" s="5">
         <v>46244.81761719908</v>
@@ -8512,7 +8509,7 @@
         <v>46244.913855798615</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8539,13 +8536,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8555,7 +8552,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B123" s="9">
         <v>46244.81762068287</v>
@@ -8565,7 +8562,7 @@
         <v>46244.913851805555</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8592,13 +8589,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8608,7 +8605,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B124" s="5">
         <v>46244.81762393519</v>
@@ -8618,7 +8615,7 @@
         <v>46244.91384795139</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8645,13 +8642,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8661,7 +8658,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B125" s="9">
         <v>46244.81762652777</v>
@@ -8671,7 +8668,7 @@
         <v>46244.91384385417</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8698,13 +8695,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8714,7 +8711,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B126" s="5">
         <v>46244.81762986111</v>
@@ -8724,7 +8721,7 @@
         <v>46244.91383961806</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8751,13 +8748,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8767,7 +8764,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B127" s="9">
         <v>46244.81768571759</v>
@@ -8777,7 +8774,7 @@
         <v>46244.91338439815</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8804,13 +8801,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q127" s="9">
         <v>46379</v>
@@ -8830,7 +8827,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B128" s="5">
         <v>46244.81769393518</v>
@@ -8840,7 +8837,7 @@
         <v>46244.91398324074</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8867,13 +8864,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8883,7 +8880,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B129" s="9">
         <v>46244.817696770835</v>
@@ -8893,7 +8890,7 @@
         <v>46244.91397908565</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8920,13 +8917,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8936,7 +8933,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B130" s="5">
         <v>46244.81770020833</v>
@@ -8946,7 +8943,7 @@
         <v>46244.913975</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8973,13 +8970,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8989,7 +8986,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B131" s="9">
         <v>46244.81770377315</v>
@@ -8999,7 +8996,7 @@
         <v>46244.91397079861</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9026,13 +9023,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9042,7 +9039,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B132" s="5">
         <v>46244.8177063426</v>
@@ -9052,7 +9049,7 @@
         <v>46244.913967071756</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9079,13 +9076,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9095,7 +9092,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B133" s="9">
         <v>46244.817751400464</v>
@@ -9105,7 +9102,7 @@
         <v>46244.913963541665</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9132,13 +9129,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9148,7 +9145,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B134" s="5">
         <v>46244.817755393524</v>
@@ -9158,7 +9155,7 @@
         <v>46244.91395974537</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9185,13 +9182,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9201,7 +9198,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B135" s="9">
         <v>46244.81775805556</v>
@@ -9211,7 +9208,7 @@
         <v>46244.91395638889</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9238,13 +9235,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9254,7 +9251,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B136" s="5">
         <v>46244.81776177083</v>
@@ -9264,7 +9261,7 @@
         <v>46244.91395271991</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9291,13 +9288,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9307,7 +9304,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B137" s="9">
         <v>46244.81781928241</v>
@@ -9317,7 +9314,7 @@
         <v>46244.913380405094</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9344,10 +9341,10 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>26</v>
@@ -9370,7 +9367,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B138" s="5">
         <v>46244.81782405093</v>
@@ -9380,7 +9377,7 @@
         <v>46244.91410258102</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9407,13 +9404,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9423,7 +9420,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B139" s="9">
         <v>46244.81782776621</v>
@@ -9433,7 +9430,7 @@
         <v>46244.91409853009</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9460,13 +9457,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9476,7 +9473,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B140" s="5">
         <v>46244.817832500004</v>
@@ -9486,7 +9483,7 @@
         <v>46244.91409476852</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9513,13 +9510,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9529,7 +9526,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B141" s="9">
         <v>46244.81783613426</v>
@@ -9539,7 +9536,7 @@
         <v>46244.914091099534</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
@@ -9566,13 +9563,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9582,7 +9579,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B142" s="5">
         <v>46244.817840069445</v>
@@ -9592,7 +9589,7 @@
         <v>46244.91408688657</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9619,13 +9616,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9635,7 +9632,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B143" s="9">
         <v>46244.81784383101</v>
@@ -9645,7 +9642,7 @@
         <v>46244.914082476855</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
@@ -9672,13 +9669,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9688,7 +9685,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B144" s="5">
         <v>46244.81784768519</v>
@@ -9698,7 +9695,7 @@
         <v>46244.91407861111</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9725,13 +9722,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9741,7 +9738,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B145" s="9">
         <v>46244.817851354164</v>
@@ -9751,7 +9748,7 @@
         <v>46244.914074375</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
@@ -9778,13 +9775,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9794,7 +9791,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B146" s="5">
         <v>46244.81785493056</v>
@@ -9804,7 +9801,7 @@
         <v>46244.91407049769</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -9831,13 +9828,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9847,7 +9844,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B147" s="9">
         <v>46244.81796724537</v>
@@ -9857,7 +9854,7 @@
         <v>46244.91337646991</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
@@ -9884,13 +9881,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q147" s="9">
         <v>46386</v>
@@ -9910,7 +9907,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B148" s="5">
         <v>46244.817975972226</v>
@@ -9920,7 +9917,7 @@
         <v>46244.914202106476</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -9947,13 +9944,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9963,7 +9960,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B149" s="9">
         <v>46244.81797934028</v>
@@ -9973,7 +9970,7 @@
         <v>46244.914198506944</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
@@ -10000,13 +9997,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10016,7 +10013,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B150" s="5">
         <v>46244.81798270834</v>
@@ -10026,7 +10023,7 @@
         <v>46244.9141949537</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10053,13 +10050,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10069,7 +10066,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B151" s="9">
         <v>46244.81798604167</v>
@@ -10079,7 +10076,7 @@
         <v>46244.9141912037</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
@@ -10106,13 +10103,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10122,7 +10119,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B152" s="5">
         <v>46244.81798946759</v>
@@ -10132,7 +10129,7 @@
         <v>46244.91418792824</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10159,13 +10156,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10175,7 +10172,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B153" s="9">
         <v>46244.81799275463</v>
@@ -10185,7 +10182,7 @@
         <v>46244.91418486111</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
@@ -10212,13 +10209,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q153" s="10"/>
       <c r="R153" s="10"/>
@@ -10228,7 +10225,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B154" s="5">
         <v>46244.81799599537</v>
@@ -10238,7 +10235,7 @@
         <v>46244.91418086806</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
@@ -10265,13 +10262,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10281,7 +10278,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B155" s="9">
         <v>46244.81799964121</v>
@@ -10291,7 +10288,7 @@
         <v>46244.9141775</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
@@ -10318,13 +10315,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10334,7 +10331,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B156" s="5">
         <v>46244.81800288195</v>
@@ -10344,7 +10341,7 @@
         <v>46244.914173240744</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10371,13 +10368,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10387,7 +10384,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B157" s="9">
         <v>46244.818105659724</v>
@@ -10397,7 +10394,7 @@
         <v>46244.909393634254</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>25</v>
@@ -10421,7 +10418,7 @@
         <v>26</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P157" s="10" t="s">
         <v>26</v>
@@ -10434,7 +10431,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B158" s="5">
         <v>46244.81810916666</v>
@@ -10444,16 +10441,16 @@
         <v>46244.91432081019</v>
       </c>
       <c r="E158" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G158" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="F158" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G158" s="6" t="s">
+      <c r="H158" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>354</v>
       </c>
       <c r="I158" s="5">
         <v>46391</v>
@@ -10471,13 +10468,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q158" s="5">
         <v>46391</v>
@@ -10497,7 +10494,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B159" s="9">
         <v>46244.81811532407</v>
@@ -10507,16 +10504,16 @@
         <v>46244.91432297454</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H159" s="10" t="s">
         <v>353</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>354</v>
       </c>
       <c r="I159" s="9">
         <v>46391</v>
@@ -10534,13 +10531,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10550,7 +10547,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B160" s="5">
         <v>46244.818118703704</v>
@@ -10560,16 +10557,16 @@
         <v>46244.91431875</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>354</v>
       </c>
       <c r="I160" s="5">
         <v>46391</v>
@@ -10587,13 +10584,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10603,7 +10600,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B161" s="9">
         <v>46244.8181217824</v>
@@ -10613,16 +10610,16 @@
         <v>46244.9143146412</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H161" s="10" t="s">
         <v>353</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>354</v>
       </c>
       <c r="I161" s="9">
         <v>46391</v>
@@ -10640,13 +10637,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10656,7 +10653,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B162" s="5">
         <v>46244.81812486111</v>
@@ -10666,16 +10663,16 @@
         <v>46244.91431086806</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>354</v>
       </c>
       <c r="I162" s="5">
         <v>46391</v>
@@ -10693,13 +10690,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10709,7 +10706,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B163" s="9">
         <v>46244.81812762731</v>
@@ -10719,16 +10716,16 @@
         <v>46244.91430675926</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H163" s="10" t="s">
         <v>353</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>354</v>
       </c>
       <c r="I163" s="9">
         <v>46391</v>
@@ -10746,13 +10743,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10762,7 +10759,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B164" s="5">
         <v>46244.81813112268</v>
@@ -10772,16 +10769,16 @@
         <v>46244.91430280093</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="H164" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>354</v>
       </c>
       <c r="I164" s="5">
         <v>46391</v>
@@ -10799,13 +10796,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10815,7 +10812,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B165" s="9">
         <v>46244.81813422454</v>
@@ -10825,16 +10822,16 @@
         <v>46244.9142987963</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H165" s="10" t="s">
         <v>353</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>354</v>
       </c>
       <c r="I165" s="9">
         <v>46391</v>
@@ -10852,13 +10849,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -10868,7 +10865,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B166" s="5">
         <v>46244.818137395836</v>
@@ -10878,16 +10875,16 @@
         <v>46244.91429494213</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="H166" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>354</v>
       </c>
       <c r="I166" s="5">
         <v>46391</v>
@@ -10905,13 +10902,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -10921,7 +10918,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B167" s="9">
         <v>46244.818140937496</v>
@@ -10931,16 +10928,16 @@
         <v>46244.91429079861</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H167" s="10" t="s">
         <v>353</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>354</v>
       </c>
       <c r="I167" s="9">
         <v>46391</v>
@@ -10958,13 +10955,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q167" s="10"/>
       <c r="R167" s="10"/>
@@ -10974,7 +10971,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B168" s="5">
         <v>46244.8182020949</v>
@@ -10984,7 +10981,7 @@
         <v>46244.91455590278</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11011,10 +11008,10 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>26</v>
@@ -11037,7 +11034,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B169" s="9">
         <v>46244.81820765046</v>
@@ -11047,7 +11044,7 @@
         <v>46244.91455376157</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>26</v>
@@ -11074,13 +11071,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11090,7 +11087,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B170" s="5">
         <v>46244.818210717596</v>
@@ -11100,7 +11097,7 @@
         <v>46244.91454974537</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11127,13 +11124,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11143,7 +11140,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B171" s="9">
         <v>46244.8182140162</v>
@@ -11153,7 +11150,7 @@
         <v>46244.91454637732</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11180,13 +11177,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11196,7 +11193,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B172" s="5">
         <v>46244.818217210646</v>
@@ -11206,7 +11203,7 @@
         <v>46244.914542928236</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11233,13 +11230,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11249,7 +11246,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B173" s="9">
         <v>46244.818220671295</v>
@@ -11259,7 +11256,7 @@
         <v>46244.914539108795</v>
       </c>
       <c r="E173" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F173" s="10" t="s">
         <v>26</v>
@@ -11286,13 +11283,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O173" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -11302,7 +11299,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B174" s="5">
         <v>46244.81822380787</v>
@@ -11312,7 +11309,7 @@
         <v>46244.914535601856</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11339,13 +11336,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -11355,7 +11352,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B175" s="9">
         <v>46244.818227094904</v>
@@ -11365,7 +11362,7 @@
         <v>46244.91453206018</v>
       </c>
       <c r="E175" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F175" s="10" t="s">
         <v>26</v>
@@ -11392,13 +11389,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O175" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -11408,7 +11405,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B176" s="5">
         <v>46244.81823046296</v>
@@ -11418,7 +11415,7 @@
         <v>46244.91452826389</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -11445,13 +11442,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -11461,7 +11458,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B177" s="9">
         <v>46244.81823376157</v>
@@ -11471,7 +11468,7 @@
         <v>46244.91452491898</v>
       </c>
       <c r="E177" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F177" s="10" t="s">
         <v>26</v>
@@ -11498,13 +11495,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O177" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -11514,7 +11511,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B178" s="5">
         <v>46244.8183515625</v>
@@ -11524,16 +11521,16 @@
         <v>46244.91482409722</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H178" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I178" s="5">
         <v>46393</v>
@@ -11551,13 +11548,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q178" s="5">
         <v>46393</v>
@@ -11577,7 +11574,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B179" s="9">
         <v>46244.8183578125</v>
@@ -11587,16 +11584,16 @@
         <v>46244.91479045139</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H179" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H179" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I179" s="9">
         <v>46393</v>
@@ -11614,13 +11611,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O179" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -11630,7 +11627,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B180" s="5">
         <v>46244.81836063658</v>
@@ -11640,16 +11637,16 @@
         <v>46244.914786828704</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H180" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I180" s="5">
         <v>46393</v>
@@ -11667,13 +11664,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -11683,7 +11680,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B181" s="9">
         <v>46244.81836416667</v>
@@ -11693,16 +11690,16 @@
         <v>46244.91478277778</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H181" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H181" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I181" s="9">
         <v>46393</v>
@@ -11720,13 +11717,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O181" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -11736,7 +11733,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B182" s="5">
         <v>46244.81836775463</v>
@@ -11746,16 +11743,16 @@
         <v>46244.914779108796</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H182" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H182" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I182" s="5">
         <v>46393</v>
@@ -11773,13 +11770,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -11789,7 +11786,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B183" s="9">
         <v>46244.81837119213</v>
@@ -11799,16 +11796,16 @@
         <v>46244.91477552083</v>
       </c>
       <c r="E183" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H183" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H183" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I183" s="9">
         <v>46393</v>
@@ -11826,13 +11823,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O183" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -11842,7 +11839,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B184" s="5">
         <v>46244.8183746412</v>
@@ -11852,16 +11849,16 @@
         <v>46244.91477159722</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H184" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I184" s="5">
         <v>46393</v>
@@ -11879,13 +11876,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -11895,7 +11892,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B185" s="9">
         <v>46244.81837791667</v>
@@ -11905,16 +11902,16 @@
         <v>46244.91476724537</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H185" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H185" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I185" s="9">
         <v>46393</v>
@@ -11932,13 +11929,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O185" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -11948,7 +11945,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B186" s="5">
         <v>46244.81838135417</v>
@@ -11958,16 +11955,16 @@
         <v>46244.91476313658</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H186" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I186" s="5">
         <v>46393</v>
@@ -11985,13 +11982,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12001,7 +11998,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B187" s="9">
         <v>46244.81838474537</v>
@@ -12011,16 +12008,16 @@
         <v>46244.914758240746</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H187" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H187" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I187" s="9">
         <v>46393</v>
@@ -12038,13 +12035,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O187" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12054,7 +12051,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B188" s="5">
         <v>46244.818483333336</v>
@@ -12064,16 +12061,16 @@
         <v>46244.9149944213</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H188" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I188" s="5">
         <v>46394</v>
@@ -12091,13 +12088,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q188" s="5">
         <v>46394</v>
@@ -12117,7 +12114,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B189" s="9">
         <v>46244.81849010417</v>
@@ -12127,16 +12124,16 @@
         <v>46244.914988275465</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H189" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H189" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I189" s="9">
         <v>46394</v>
@@ -12154,13 +12151,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O189" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P189" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q189" s="10"/>
       <c r="R189" s="10"/>
@@ -12170,7 +12167,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B190" s="5">
         <v>46244.818493750005</v>
@@ -12180,16 +12177,16 @@
         <v>46244.91498451389</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H190" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H190" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I190" s="5">
         <v>46394</v>
@@ -12207,13 +12204,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -12223,7 +12220,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B191" s="9">
         <v>46244.81849773148</v>
@@ -12233,16 +12230,16 @@
         <v>46244.91498094908</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F191" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H191" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H191" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I191" s="9">
         <v>46394</v>
@@ -12260,13 +12257,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O191" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P191" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q191" s="10"/>
       <c r="R191" s="10"/>
@@ -12276,7 +12273,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B192" s="5">
         <v>46244.818501284724</v>
@@ -12286,16 +12283,16 @@
         <v>46244.91497737268</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H192" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I192" s="5">
         <v>46394</v>
@@ -12313,13 +12310,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -12329,7 +12326,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B193" s="9">
         <v>46244.81850474537</v>
@@ -12339,16 +12336,16 @@
         <v>46244.914973680556</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H193" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H193" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I193" s="9">
         <v>46394</v>
@@ -12366,13 +12363,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O193" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P193" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q193" s="10"/>
       <c r="R193" s="10"/>
@@ -12382,7 +12379,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B194" s="5">
         <v>46244.818508055556</v>
@@ -12392,16 +12389,16 @@
         <v>46244.914969687496</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H194" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I194" s="5">
         <v>46394</v>
@@ -12419,13 +12416,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -12435,7 +12432,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B195" s="9">
         <v>46244.818511192134</v>
@@ -12445,16 +12442,16 @@
         <v>46244.91496552083</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F195" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H195" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H195" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I195" s="9">
         <v>46394</v>
@@ -12472,13 +12469,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O195" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P195" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q195" s="10"/>
       <c r="R195" s="10"/>
@@ -12488,7 +12485,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B196" s="5">
         <v>46244.81851430556</v>
@@ -12498,16 +12495,16 @@
         <v>46244.91496141204</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H196" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I196" s="5">
         <v>46394</v>
@@ -12525,13 +12522,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -12541,7 +12538,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B197" s="9">
         <v>46244.81851734954</v>
@@ -12551,16 +12548,16 @@
         <v>46244.91495744213</v>
       </c>
       <c r="E197" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F197" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H197" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H197" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I197" s="9">
         <v>46394</v>
@@ -12578,13 +12575,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O197" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P197" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q197" s="10"/>
       <c r="R197" s="10"/>
@@ -12594,7 +12591,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B198" s="5">
         <v>46244.81857152778</v>
@@ -12604,7 +12601,7 @@
         <v>46244.909651319445</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>25</v>
@@ -12628,7 +12625,7 @@
         <v>26</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>26</v>
@@ -12641,7 +12638,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B199" s="9">
         <v>46244.81857427083</v>
@@ -12651,16 +12648,16 @@
         <v>46244.91504364583</v>
       </c>
       <c r="E199" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="F199" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G199" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="F199" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G199" s="10" t="s">
+      <c r="H199" s="10" t="s">
         <v>412</v>
-      </c>
-      <c r="H199" s="10" t="s">
-        <v>413</v>
       </c>
       <c r="I199" s="9">
         <v>46395</v>
@@ -12678,13 +12675,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O199" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P199" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q199" s="9">
         <v>46405</v>
@@ -12704,7 +12701,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B200" s="5">
         <v>46244.81869961806</v>
@@ -12714,16 +12711,16 @@
         <v>46244.915039988424</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>412</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>413</v>
       </c>
       <c r="I200" s="5">
         <v>46395</v>
@@ -12741,13 +12738,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q200" s="5">
         <v>46405</v>
